--- a/GourmetProject/GameConfig/Datas/dish_variant.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish_variant.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,148 +476,170 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>菜品变体ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>引用的菜品基础ID</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>唯一A标签ID</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>唯一B标签ID</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>出现隐藏分下限</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>出现隐藏分上限</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>随机基础权重</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>商店价格</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>最大刷新出现次数</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>固有标签ID列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>list,string</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>rice</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>rice</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" t="n">
-        <v>150</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>egg</t>
+          <t>rice</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>egg</t>
+          <t>rice</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>t_fresh</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>soup</t>
+          <t>egg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>soup</t>
+          <t>egg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -627,7 +649,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>t_lonely</t>
+          <t>t_fresh</t>
         </is>
       </c>
     </row>
@@ -635,34 +657,34 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>soup</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>soup</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>t_fresh</t>
+          <t>t_lonely</t>
         </is>
       </c>
     </row>
@@ -670,34 +692,34 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>noodle</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>noodle</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H7" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>t_hearty</t>
+          <t>t_fresh</t>
         </is>
       </c>
     </row>
@@ -705,21 +727,21 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dumpling</t>
+          <t>noodle</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dumpling</t>
+          <t>noodle</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H8" t="n">
         <v>90</v>
@@ -740,34 +762,34 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>chili</t>
+          <t>dumpling</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>chili</t>
+          <t>dumpling</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H9" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>t_spicy</t>
+          <t>t_hearty</t>
         </is>
       </c>
     </row>
@@ -775,34 +797,34 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>chili</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>chili</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="H10" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>t_sweet</t>
+          <t>t_spicy</t>
         </is>
       </c>
     </row>
@@ -810,30 +832,30 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>30</v>
       </c>
-      <c r="G11" t="n">
-        <v>50</v>
-      </c>
       <c r="H11" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -845,32 +867,67 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>feast</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>feast</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H12" t="n">
+        <v>60</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>t_sweet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>feast</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>feast</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
         <v>40</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G13" t="n">
         <v>70</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H13" t="n">
         <v>40</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>8</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>t_feast</t>
         </is>
